--- a/RECETAS_CUSCO_GRAMOS_ML.xlsx
+++ b/RECETAS_CUSCO_GRAMOS_ML.xlsx
@@ -30,12 +30,17 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -65,11 +70,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -144,6 +150,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="H1024" authorId="0" shapeId="0">
+      <text>
+        <t>Corregido: en Odoo decía 10 KILOS; según el costo en Inforest son 10 gramos.</t>
+      </text>
+    </comment>
+    <comment ref="H1183" authorId="0" shapeId="0">
+      <text>
+        <t>Corregido: en Odoo decía 20 KILOS; según el costo en Inforest son 20 gramos.</t>
+      </text>
+    </comment>
+    <comment ref="H1395" authorId="0" shapeId="0">
+      <text>
+        <t>Corregido: en Odoo decía 150 KILOS; según el costo en Inforest son 150 gramos.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24099,8 +24130,8 @@
           <t>RB SALSA GOLF</t>
         </is>
       </c>
-      <c r="H1024" t="n">
-        <v>10000</v>
+      <c r="H1024" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="1025">
@@ -27459,8 +27490,8 @@
           <t>RB SALSA GOLF</t>
         </is>
       </c>
-      <c r="H1183" t="n">
-        <v>20000</v>
+      <c r="H1183" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="1184">
@@ -31799,8 +31830,8 @@
           <t>RB BASE YASAYTAME</t>
         </is>
       </c>
-      <c r="H1395" t="n">
-        <v>150000</v>
+      <c r="H1395" s="2" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="1396">
@@ -35385,5 +35416,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>